--- a/config/held_item/effect.xlsx
+++ b/config/held_item/effect.xlsx
@@ -1340,7 +1340,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇</t>
+          <t>HP提升%s</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>物攻が%s上昇</t>
+          <t>物攻上升%s</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>特防が%s上昇</t>
+          <t>特防上升%s</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>特攻が%s上昇</t>
+          <t>特攻上升%s</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>物防が%s上昇</t>
+          <t>物防上升%s</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>速度が%s上昇</t>
+          <t>速度提升%s</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇、物防が%s上昇</t>
+          <t>HP上升%s，物防上升%s</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇、特防が%s上昇</t>
+          <t>HP上升%s，特防上升%s</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>物防が%s上昇、特防が%s上昇</t>
+          <t>物防上升%s，特防上升%s</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>物攻が%s上昇、会心率が%s上昇</t>
+          <t>物攻上升%s，暴击率上升%s</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>特攻が%s上昇、会心率が%s上昇</t>
+          <t>特攻%s上升，暴击率%s上升</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇、物攻が%s上昇</t>
+          <t>HP上升%s，物攻上升%s</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇、特攻が%s上昇</t>
+          <t>HP提升%s、特攻提升%s</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>速度が%s上昇</t>
+          <t>速度提升%s</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>会心率が%s上昇</t>
+          <t>暴击率上升%s</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇</t>
+          <t>HP提升%s</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>膨大な溶岩エネルギーを蓄えた箱。\n速度が%s上昇</t>
+          <t>储存著庞大熔岩能量的箱子。\n速度提升%s</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>膨大な電気エネルギーを蓄えた箱。\n速度が%s上昇</t>
+          <t>储存了大量电能的箱子。\n速度提升%s</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>速度が%s上昇</t>
+          <t>速度提升%s</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>物防が%s上昇、特防が%s上昇</t>
+          <t>物防上升%s，特防上升%s</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇</t>
+          <t>HP提升%s</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇、速度が%s上昇</t>
+          <t>HP提升%s、速度提升%s</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇、速度が%s上昇</t>
+          <t>HP提升%s、速度提升%s</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇、速度が%s上昇</t>
+          <t>HP提升%s、速度提升%s</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇、速度が%s上昇</t>
+          <t>HP提升%s、速度提升%s</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇、速度が%s上昇</t>
+          <t>HP提升%s、速度提升%s</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>HPが%s上昇、速度が%s上昇</t>
+          <t>HP提升%s、速度提升%s</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>特攻ダメージバフが%s上昇、特防無視が%s上昇</t>
+          <t>特攻伤害提升%s、特防无视提升%s</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>物攻ダメージバフが%s上昇、物防無視が%s上昇</t>
+          <t>物攻伤害增益提升%s，物防无视提升%s</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>【%s】シリーズ雷属性スキルダメージバフが追加で%s上昇</t>
+          <t>【%s】系列雷属性技能伤害增益增加%s上升</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>【%s】シリーズ物攻が追加で%s上昇</t>
+          <t>【%s】系列物攻追加%s上升</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>炎属性スキルダメージバフが追加で%s上昇</t>
+          <t>火焰属性技能伤害增益额外提升%s</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>雷属性スキルダメージバフが追加で%s上昇</t>
+          <t>雷属性技能伤害增益额外提升%s</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>装備後、物攻が%s増加</t>
+          <t>装备后，物攻增加%s</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>会心率が%s上昇、会心ダメージが%s上昇</t>
+          <t>暴击率上升%s，暴击伤害上升%s</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>抵抗が%s上昇、抵抗力が%s上昇</t>
+          <t>阻力上升%s，阻力上升%s</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>HPが%s上昇、治癒率が%s上昇</t>
+          <t>HP提升%s，治愈率提升%s</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>会心率が%s上昇、特防無視が%s上昇</t>
+          <t>暴击率上升%s，特防无视上升%s</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>HPが%s上昇、会心耐性が%s上昇</t>
+          <t>HP提升%s，暴击抵抗提升%s</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>物攻が%s上昇、吸血が%s上昇</t>
+          <t>物攻上升%s，吸血上升%s</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>HPが%s上昇、ダメージ耐性が%s上昇</t>
+          <t>HP提升%s、伤害减免提升%s</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>特攻が%s上昇、速度が%s上昇</t>
+          <t>特攻提升%s，速度提升%s</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>ダメージ耐性が%s上昇、特防が%s上昇</t>
+          <t>伤害减免提升%s、特防提升%s</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>物攻が%s上昇、特攻が%s上昇</t>
+          <t>物攻上升%s，特攻上升%s</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>HPが%s上昇、ダメージバフが%s上昇</t>
+          <t>HP上升%s，伤害增益上升%s</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>物防が%s上昇、ダメージ耐性が%s上昇</t>
+          <t>物防提升%s，伤害减免提升%s</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>致命耐性が%s上昇、覚醒値の回復速度が%s上昇</t>
+          <t>致命耐性提升%s，觉醒值回复速度提升%s</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>PvPダメージバフが%s上昇、PvPダメージ耐性が%s上昇</t>
+          <t>PvP伤害增益提升%s，PvP伤害抗性提升%s</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>会心率が%s上昇、会心ダメージが%s上昇</t>
+          <t>暴击率上升%s，暴击伤害上升%s</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>抵抗率が%s上昇、特防が%s上昇</t>
+          <t>抵抗率上升%s，特防上升%s</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>治癒率が%s上昇、致命耐性が%s上昇</t>
+          <t>治愈率提高%s，致命耐性提高%s</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>致命ダメージバフが%s上昇、吸血が%s上昇</t>
+          <t>致命伤害提升%s，吸血提升%s</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>HPが%s上昇、反撃が%s上昇</t>
+          <t>HP上升%s，反击上升%s</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>HPが%s上昇、致命ダメージ上昇が%s上昇</t>
+          <t>HP上升%s，致命伤害上升%s</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>真実の光線を映し出す不思議な鏡。\nHPが%s上昇</t>
+          <t>映照出真实光线的不可思议的镜子。\nHP上升%s</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>特攻が%s上昇</t>
+          <t>特攻上升%s</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>ダメージバフが%s上昇、制御率が%s上昇</t>
+          <t>伤害增益提升%s，控制率提升%s</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>ダメージ耐性が%s上昇、会心耐性が%s上昇</t>
+          <t>伤害减免提升%s，暴击抵抗提升%s</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>抵抗率が%s上昇、致命耐性が%s上昇</t>
+          <t>抗性提高%s，致命抗性提高%s</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>特攻が%s上昇、吸血が%s上昇</t>
+          <t>特攻%s上升，吸血%s上升</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>HPが%s上昇、制御耐性が%s上昇</t>
+          <t>HP提升%s、控制耐性提升%s</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>HPが%s上昇、制御耐性が%s上昇</t>
+          <t>HP提升%s、控制耐性提升%s</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>致命ダメージバフが%s上昇、覚醒値の回復速度が%s上昇</t>
+          <t>致命伤害增益提升%s，觉醒值回复速度提升%s</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>HPが%s上昇、致命ダメージ耐性が%s上昇</t>
+          <t>HP提升%s，致命伤害减免提升%s</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
